--- a/STORES.xlsx
+++ b/STORES.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AG_WORK\yoidore-quest2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8EA67DA-1C8A-4F31-87E3-69CD27F0B2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DE99DA-84ED-4A8D-AEF5-277DD8474D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="店舗一覧 (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">店舗一覧!$A$1:$W$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">店舗一覧!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="493">
   <si>
     <t>ID</t>
   </si>
@@ -1101,10 +1101,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ダイニング</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>イベント限定ミニバーガー+ドリンク1杯</t>
   </si>
   <si>
@@ -1357,9 +1353,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>遊べる・エンタメ</t>
-  </si>
-  <si>
     <t>002.jpg</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1901,10 +1894,6 @@
     <t>ピッツァ前菜ワインセット</t>
   </si>
   <si>
-    <t>しっかりご飯</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>サク飲み</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1938,6 +1927,79 @@
     <t>クエスト内容</t>
     <rPh sb="4" eb="6">
       <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スタイル</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>中華</t>
+    <rPh sb="0" eb="2">
+      <t>チュウカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テーブルあり</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カウンター</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>イタリアン・メキシカン・アメリカン・和食</t>
+    <rPh sb="18" eb="20">
+      <t>ワショク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>イタリアン・ワイン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>沖縄料理</t>
+    <rPh sb="0" eb="2">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>リョウリ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>腹ごしらえ</t>
+    <rPh sb="0" eb="1">
+      <t>ハラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>夜遊び</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テイクアウト</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テイクアウト専門</t>
+    <rPh sb="6" eb="8">
+      <t>センモン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テイクアウトOK</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>テイクアウト不可</t>
+    <rPh sb="6" eb="8">
+      <t>フカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2045,7 +2107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2072,9 +2134,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2378,23 +2437,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X34"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.5" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.5" style="8" customWidth="1"/>
-    <col min="6" max="6" width="22.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="20" width="10.5" style="8" customWidth="1"/>
-    <col min="21" max="21" width="44.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="39.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.625" style="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="8"/>
+    <col min="3" max="3" width="10.5" style="8" customWidth="1"/>
+    <col min="4" max="4" width="26.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="8" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="8" customWidth="1"/>
+    <col min="8" max="8" width="22.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="10.5" style="8" customWidth="1"/>
+    <col min="12" max="12" width="16.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="21" width="10.5" style="8" customWidth="1"/>
+    <col min="22" max="22" width="44.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="39.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2408,67 +2472,70 @@
         <v>4</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="6" t="s">
+      <c r="R1" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="X1" s="6" t="s">
-        <v>376</v>
+      <c r="Y1" s="6" t="s">
+        <v>374</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>24</v>
       </c>
@@ -2482,40 +2549,40 @@
         <v>28</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="8">
+      <c r="N2" s="8">
         <v>800</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="M2" s="8" t="s">
+      <c r="P2" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="Q2" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="P2" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="R2" s="8" t="s">
         <v>40</v>
@@ -2523,23 +2590,26 @@
       <c r="S2" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="T2" s="8" t="s">
-        <v>42</v>
+      <c r="T2" s="8">
+        <v>0</v>
       </c>
       <c r="U2" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="W2" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="W2" s="9" t="s">
+      <c r="X2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="X2" s="9" t="s">
-        <v>377</v>
+      <c r="Y2" s="9" t="s">
+        <v>375</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
         <v>46</v>
       </c>
@@ -2553,40 +2623,46 @@
         <v>267</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="F3" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="I3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="N3" s="8">
         <v>1000</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>410</v>
-      </c>
       <c r="V3" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="W3" s="9" t="s">
-        <v>312</v>
+        <v>408</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>311</v>
       </c>
       <c r="X3" s="9" t="s">
-        <v>378</v>
+        <v>310</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>376</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>64</v>
       </c>
@@ -2600,40 +2676,46 @@
         <v>272</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F4" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>280</v>
-      </c>
-      <c r="I4" s="8">
+      <c r="I4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="N4" s="8">
         <v>1000</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" s="8" t="s">
-        <v>411</v>
-      </c>
       <c r="V4" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>345</v>
+        <v>409</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>312</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>379</v>
+        <v>343</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
         <v>79</v>
       </c>
@@ -2644,43 +2726,49 @@
         <v>242</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>477</v>
-      </c>
       <c r="F5" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="I5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="N5" s="8">
         <v>1000</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>412</v>
-      </c>
       <c r="V5" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="W5" s="9" t="s">
-        <v>375</v>
+        <v>410</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>313</v>
       </c>
       <c r="X5" s="9" t="s">
-        <v>380</v>
+        <v>373</v>
+      </c>
+      <c r="Y5" s="9" t="s">
+        <v>378</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
         <v>96</v>
       </c>
@@ -2694,45 +2782,51 @@
         <v>268</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="I6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="N6" s="8">
         <v>1000</v>
       </c>
-      <c r="K6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U6" s="8" t="s">
-        <v>413</v>
-      </c>
       <c r="V6" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="W6" s="9" t="s">
-        <v>346</v>
+        <v>411</v>
+      </c>
+      <c r="W6" s="8" t="s">
+        <v>314</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>381</v>
+        <v>344</v>
+      </c>
+      <c r="Y6" s="9" t="s">
+        <v>379</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
         <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>239</v>
@@ -2740,41 +2834,47 @@
       <c r="D7" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>283</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="I7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="N7" s="8">
         <v>1000</v>
       </c>
-      <c r="K7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>414</v>
-      </c>
       <c r="V7" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="W7" s="9" t="s">
-        <v>347</v>
+        <v>412</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>382</v>
+        <v>345</v>
+      </c>
+      <c r="Y7" s="9" t="s">
+        <v>380</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>124</v>
       </c>
@@ -2787,41 +2887,47 @@
       <c r="D8" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>284</v>
-      </c>
       <c r="I8" s="8" t="s">
-        <v>442</v>
-      </c>
-      <c r="K8" s="8" t="s">
         <v>34</v>
       </c>
+      <c r="J8" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="L8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>415</v>
+        <v>448</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>440</v>
       </c>
       <c r="V8" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="W8" s="9" t="s">
-        <v>348</v>
+        <v>413</v>
+      </c>
+      <c r="W8" s="8" t="s">
+        <v>316</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>383</v>
+        <v>346</v>
+      </c>
+      <c r="Y8" s="9" t="s">
+        <v>381</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8" t="s">
         <v>140</v>
       </c>
@@ -2834,41 +2940,47 @@
       <c r="D9" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>285</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="I9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="N9" s="8">
         <v>1000</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U9" s="8" t="s">
-        <v>429</v>
-      </c>
       <c r="V9" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="W9" s="9" t="s">
-        <v>349</v>
+        <v>427</v>
+      </c>
+      <c r="W9" s="8" t="s">
+        <v>317</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>384</v>
+        <v>347</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>382</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8" t="s">
         <v>150</v>
       </c>
@@ -2882,40 +2994,46 @@
         <v>275</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F10" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>452</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="I10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="N10" s="8">
         <v>1000</v>
       </c>
-      <c r="K10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U10" s="8" t="s">
-        <v>430</v>
-      </c>
       <c r="V10" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="W10" s="9" t="s">
-        <v>350</v>
+        <v>428</v>
+      </c>
+      <c r="W10" s="8" t="s">
+        <v>318</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>385</v>
+        <v>348</v>
+      </c>
+      <c r="Y10" s="9" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>162</v>
       </c>
@@ -2929,40 +3047,46 @@
         <v>273</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F11" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>287</v>
-      </c>
-      <c r="I11" s="8">
+      <c r="I11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="N11" s="8">
         <v>800</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U11" s="8" t="s">
-        <v>435</v>
-      </c>
       <c r="V11" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>351</v>
+        <v>433</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>319</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>386</v>
+        <v>349</v>
+      </c>
+      <c r="Y11" s="9" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A12" s="8" t="s">
         <v>244</v>
       </c>
@@ -2973,43 +3097,49 @@
         <v>242</v>
       </c>
       <c r="D12" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>477</v>
-      </c>
       <c r="F12" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="I12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="N12" s="8">
         <v>1000</v>
       </c>
-      <c r="K12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U12" s="8" t="s">
-        <v>428</v>
-      </c>
       <c r="V12" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="W12" s="9" t="s">
-        <v>352</v>
+        <v>426</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>320</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>387</v>
+        <v>350</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>385</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A13" s="8" t="s">
         <v>245</v>
       </c>
@@ -3023,40 +3153,46 @@
         <v>273</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>443</v>
+        <v>474</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="I13" s="8">
+        <v>441</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="N13" s="8">
         <v>1000</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U13" s="8" t="s">
-        <v>422</v>
-      </c>
       <c r="V13" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="W13" s="9" t="s">
-        <v>353</v>
+        <v>420</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>321</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>388</v>
+        <v>351</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>386</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A14" s="8" t="s">
         <v>246</v>
       </c>
@@ -3070,40 +3206,46 @@
         <v>273</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F14" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>456</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="I14" s="8">
+      <c r="I14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="N14" s="8">
         <v>800</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U14" s="8" t="s">
-        <v>416</v>
-      </c>
       <c r="V14" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>354</v>
+        <v>414</v>
+      </c>
+      <c r="W14" s="8" t="s">
+        <v>322</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>389</v>
+        <v>352</v>
+      </c>
+      <c r="Y14" s="9" t="s">
+        <v>387</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>247</v>
       </c>
@@ -3117,40 +3259,46 @@
         <v>275</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F15" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>291</v>
-      </c>
-      <c r="I15" s="8">
+      <c r="I15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="N15" s="8">
         <v>1000</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U15" s="8" t="s">
-        <v>423</v>
-      </c>
       <c r="V15" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>355</v>
+        <v>421</v>
+      </c>
+      <c r="W15" s="8" t="s">
+        <v>323</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>390</v>
+        <v>353</v>
+      </c>
+      <c r="Y15" s="9" t="s">
+        <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A16" s="8" t="s">
         <v>248</v>
       </c>
@@ -3161,43 +3309,49 @@
         <v>239</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>458</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="I16" s="8">
+      <c r="I16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="N16" s="8">
         <v>1600</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>438</v>
-      </c>
       <c r="V16" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="W16" s="9" t="s">
-        <v>356</v>
+        <v>436</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>324</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>391</v>
+        <v>354</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>389</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A17" s="8" t="s">
         <v>249</v>
       </c>
@@ -3211,40 +3365,46 @@
         <v>28</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="I17" s="8">
+      <c r="I17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="N17" s="8">
         <v>1000</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>432</v>
-      </c>
       <c r="V17" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="W17" s="9" t="s">
-        <v>357</v>
+        <v>430</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>325</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>392</v>
+        <v>355</v>
+      </c>
+      <c r="Y17" s="9" t="s">
+        <v>390</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
         <v>250</v>
       </c>
@@ -3257,41 +3417,47 @@
       <c r="D18" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="F18" s="8" t="s">
+      <c r="E18" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>460</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="I18" s="8">
+      <c r="I18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="N18" s="8">
         <v>1000</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U18" s="8" t="s">
-        <v>424</v>
-      </c>
       <c r="V18" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="W18" s="9" t="s">
-        <v>358</v>
+        <v>422</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>326</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>393</v>
+        <v>356</v>
+      </c>
+      <c r="Y18" s="9" t="s">
+        <v>391</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A19" s="8" t="s">
         <v>251</v>
       </c>
@@ -3305,45 +3471,51 @@
         <v>271</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F19" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>461</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>295</v>
-      </c>
-      <c r="I19" s="8">
+      <c r="I19" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="N19" s="8">
         <v>1000</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U19" s="8" t="s">
-        <v>433</v>
-      </c>
       <c r="V19" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="W19" s="9" t="s">
-        <v>359</v>
+        <v>431</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>327</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>394</v>
+        <v>357</v>
+      </c>
+      <c r="Y19" s="9" t="s">
+        <v>392</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="71.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A20" s="8" t="s">
         <v>252</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>241</v>
@@ -3351,44 +3523,50 @@
       <c r="D20" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F20" s="8" t="s">
+      <c r="E20" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="I20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L20" s="8" t="s">
+      <c r="J20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="P20" s="8">
+      <c r="R20" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="T20" s="8">
         <v>300</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="U20" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="R20" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="S20" s="11" t="s">
-        <v>480</v>
-      </c>
-      <c r="U20" s="8" t="s">
-        <v>436</v>
-      </c>
       <c r="V20" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="W20" s="9" t="s">
-        <v>360</v>
+        <v>434</v>
+      </c>
+      <c r="W20" s="8" t="s">
+        <v>328</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>395</v>
+        <v>358</v>
+      </c>
+      <c r="Y20" s="9" t="s">
+        <v>393</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A21" s="8" t="s">
         <v>253</v>
       </c>
@@ -3402,40 +3580,46 @@
         <v>272</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="F21" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="I21" s="8">
+      <c r="I21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="N21" s="8">
         <v>500</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U21" s="8" t="s">
-        <v>434</v>
-      </c>
       <c r="V21" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="W21" s="9" t="s">
-        <v>361</v>
+        <v>432</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>329</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>396</v>
+        <v>359</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>394</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>254</v>
       </c>
@@ -3449,40 +3633,46 @@
         <v>271</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F22" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="8" t="s">
-        <v>463</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I22" s="8">
+      <c r="I22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="N22" s="8">
         <v>1000</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U22" s="8" t="s">
-        <v>431</v>
-      </c>
       <c r="V22" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="W22" s="9" t="s">
-        <v>362</v>
+        <v>429</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>330</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>397</v>
+        <v>360</v>
+      </c>
+      <c r="Y22" s="9" t="s">
+        <v>395</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A23" s="8" t="s">
         <v>255</v>
       </c>
@@ -3496,40 +3686,46 @@
         <v>276</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F23" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>298</v>
-      </c>
-      <c r="I23" s="8">
+      <c r="I23" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="N23" s="8">
         <v>1000</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U23" s="8" t="s">
-        <v>425</v>
-      </c>
       <c r="V23" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="W23" s="9" t="s">
-        <v>363</v>
+        <v>423</v>
+      </c>
+      <c r="W23" s="8" t="s">
+        <v>331</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>398</v>
+        <v>361</v>
+      </c>
+      <c r="Y23" s="9" t="s">
+        <v>396</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A24" s="8" t="s">
         <v>256</v>
       </c>
@@ -3543,40 +3739,46 @@
         <v>272</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F24" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="G24" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="I24" s="8">
+      <c r="I24" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="N24" s="8">
         <v>1000</v>
       </c>
-      <c r="K24" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>427</v>
-      </c>
       <c r="V24" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="W24" s="9" t="s">
-        <v>364</v>
+        <v>425</v>
+      </c>
+      <c r="W24" s="8" t="s">
+        <v>332</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>399</v>
+        <v>362</v>
+      </c>
+      <c r="Y24" s="9" t="s">
+        <v>397</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A25" s="8" t="s">
         <v>257</v>
       </c>
@@ -3590,42 +3792,48 @@
         <v>273</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F25" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="I25" s="8">
+      <c r="I25" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="N25" s="8">
         <v>1000</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="V25" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="W25" s="9" t="s">
-        <v>365</v>
+      <c r="W25" s="8" t="s">
+        <v>333</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>400</v>
+        <v>363</v>
+      </c>
+      <c r="Y25" s="9" t="s">
+        <v>398</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A26" s="8" t="s">
         <v>258</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>242</v>
@@ -3634,37 +3842,43 @@
         <v>273</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F26" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>467</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="I26" s="8">
+      <c r="I26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="N26" s="8">
         <v>800</v>
       </c>
-      <c r="K26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="V26" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="W26" s="9" t="s">
-        <v>366</v>
+      <c r="W26" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>401</v>
+        <v>364</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>399</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A27" s="8" t="s">
         <v>259</v>
       </c>
@@ -3678,40 +3892,46 @@
         <v>273</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F27" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="I27" s="8">
+      <c r="I27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="N27" s="8">
         <v>1000</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U27" s="8" t="s">
-        <v>426</v>
-      </c>
       <c r="V27" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="W27" s="9" t="s">
-        <v>367</v>
+        <v>424</v>
+      </c>
+      <c r="W27" s="8" t="s">
+        <v>335</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>402</v>
+        <v>365</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>400</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A28" s="8" t="s">
         <v>260</v>
       </c>
@@ -3724,41 +3944,47 @@
       <c r="D28" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="E28" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F28" s="8" t="s">
+      <c r="E28" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G28" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="I28" s="8">
+      <c r="I28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="N28" s="8">
         <v>1000</v>
       </c>
-      <c r="K28" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U28" s="8" t="s">
-        <v>421</v>
-      </c>
       <c r="V28" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="W28" s="9" t="s">
-        <v>368</v>
+        <v>419</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>403</v>
+        <v>366</v>
+      </c>
+      <c r="Y28" s="9" t="s">
+        <v>401</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A29" s="8" t="s">
         <v>261</v>
       </c>
@@ -3769,43 +3995,49 @@
         <v>242</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="F29" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H29" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="I29" s="8">
+      <c r="I29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="N29" s="8">
         <v>1000</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U29" s="8" t="s">
-        <v>418</v>
-      </c>
       <c r="V29" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="W29" s="9" t="s">
-        <v>369</v>
+        <v>416</v>
+      </c>
+      <c r="W29" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>404</v>
+        <v>367</v>
+      </c>
+      <c r="Y29" s="9" t="s">
+        <v>402</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>262</v>
       </c>
@@ -3816,43 +4048,49 @@
         <v>240</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>273</v>
+        <v>486</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F30" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="I30" s="8">
+      <c r="I30" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="N30" s="8">
         <v>1000</v>
       </c>
-      <c r="K30" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>420</v>
-      </c>
       <c r="V30" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="W30" s="9" t="s">
-        <v>370</v>
+        <v>418</v>
+      </c>
+      <c r="W30" s="8" t="s">
+        <v>338</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>405</v>
+        <v>368</v>
+      </c>
+      <c r="Y30" s="9" t="s">
+        <v>403</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>263</v>
       </c>
@@ -3865,41 +4103,47 @@
       <c r="D31" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="E31" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="F31" s="8" t="s">
+      <c r="E31" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H31" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="G31" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="I31" s="8">
+      <c r="I31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="N31" s="8">
         <v>1000</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>419</v>
-      </c>
       <c r="V31" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="W31" s="9" t="s">
-        <v>371</v>
+        <v>417</v>
+      </c>
+      <c r="W31" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>406</v>
+        <v>369</v>
+      </c>
+      <c r="Y31" s="9" t="s">
+        <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>264</v>
       </c>
@@ -3913,40 +4157,46 @@
         <v>273</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F32" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="G32" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="I32" s="8">
+      <c r="I32" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="N32" s="8">
         <v>1000</v>
       </c>
-      <c r="K32" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U32" s="8" t="s">
-        <v>417</v>
-      </c>
       <c r="V32" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="W32" s="9" t="s">
-        <v>372</v>
+        <v>415</v>
+      </c>
+      <c r="W32" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>407</v>
+        <v>370</v>
+      </c>
+      <c r="Y32" s="9" t="s">
+        <v>405</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>265</v>
       </c>
@@ -3957,43 +4207,49 @@
         <v>241</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>278</v>
+        <v>484</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="F33" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H33" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G33" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="I33" s="8">
+      <c r="I33" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="N33" s="8">
         <v>1000</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U33" s="8" t="s">
-        <v>440</v>
-      </c>
       <c r="V33" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="W33" s="9" t="s">
-        <v>373</v>
+        <v>438</v>
+      </c>
+      <c r="W33" s="8" t="s">
+        <v>341</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>408</v>
+        <v>371</v>
+      </c>
+      <c r="Y33" s="9" t="s">
+        <v>406</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>266</v>
       </c>
@@ -4004,44 +4260,50 @@
         <v>243</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>278</v>
+        <v>485</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F34" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="H34" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="G34" s="8" t="s">
-        <v>475</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>309</v>
-      </c>
-      <c r="I34" s="8">
+      <c r="I34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="N34" s="8">
         <v>800</v>
       </c>
-      <c r="K34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>439</v>
-      </c>
       <c r="V34" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="W34" s="9" t="s">
-        <v>374</v>
+        <v>437</v>
+      </c>
+      <c r="W34" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>409</v>
+        <v>372</v>
+      </c>
+      <c r="Y34" s="9" t="s">
+        <v>407</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:X34" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
